--- a/Result/CO2_ver551_000.xlsx
+++ b/Result/CO2_ver551_000.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>413181000</v>
+        <v>7913440000</v>
       </c>
       <c r="C2" t="n">
-        <v>6905703.521681963</v>
+        <v>207171104.1953748</v>
       </c>
       <c r="D2" t="n">
-        <v>5190165.43845242</v>
+        <v>155704963.1402081</v>
       </c>
       <c r="E2" t="n">
-        <v>458038.9243874723</v>
+        <v>13741167.73161347</v>
       </c>
       <c r="F2" t="n">
-        <v>2929474.370415252</v>
+        <v>87884232.67897314</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>131678900</v>
+        <v>3060554000</v>
       </c>
       <c r="C3" t="n">
-        <v>1639415.368456199</v>
+        <v>49182460.70824871</v>
       </c>
       <c r="D3" t="n">
-        <v>33746.3461214907</v>
+        <v>1012390.383557825</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -502,11 +502,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72933300</v>
+        <v>2146910000</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>33746.3461214907</v>
+        <v>1012390.383557825</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36076600</v>
+        <v>480756000</v>
       </c>
       <c r="C5" t="n">
-        <v>1639415.368456199</v>
+        <v>49182460.70824871</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2040000</v>
+        <v>2960000</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6230000</v>
+        <v>134000000</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>510000</v>
+        <v>740000</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4135000</v>
+        <v>68480000</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9754000</v>
+        <v>226708000</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -605,14 +605,14 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>19999.96704199498</v>
+        <v>599999.0070457048</v>
       </c>
       <c r="D11" t="n">
-        <v>4651.91852797233</v>
+        <v>139557.5558271913</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>5340.16911214894</v>
+        <v>160205.0762200857</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>76.83799064755335</v>
+        <v>2305.139703236254</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>10.75731869065747</v>
+        <v>322.7195584530755</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1639415.368456199</v>
+        <v>49182460.70824871</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -741,7 +741,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>99120.60442860896</v>
+        <v>2973618.132858273</v>
       </c>
       <c r="F19" t="inlineStr"/>
     </row>
@@ -755,7 +755,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>91354.56358148024</v>
+        <v>2740636.907444562</v>
       </c>
       <c r="F20" t="inlineStr"/>
     </row>
@@ -769,7 +769,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>267563.7563773831</v>
+        <v>8026912.691310637</v>
       </c>
       <c r="F21" t="inlineStr"/>
     </row>
